--- a/packages/模块进度.xlsx
+++ b/packages/模块进度.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\project\js\AnJsflScript-ts\packages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE13338-8062-4C01-9769-EFF360047EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D17D22-FF67-45F4-B08A-C4330A2BFA39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="25720" windowHeight="13800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9977,14 +9977,14 @@
         <v>168</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="9"/>
+      <c r="F14" s="5"/>
     </row>
     <row r="15" spans="3:6" ht="19.5">
       <c r="C15" s="1" t="s">
         <v>487</v>
       </c>
       <c r="E15" s="5"/>
-      <c r="F15" s="9"/>
+      <c r="F15" s="5"/>
     </row>
     <row r="16" spans="3:6" ht="19.5">
       <c r="C16" s="1" t="s">
@@ -10048,7 +10048,7 @@
         <v>176</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="9"/>
+      <c r="F25" s="5"/>
     </row>
     <row r="26" spans="3:6" ht="19.5">
       <c r="C26" s="1" t="s">
@@ -11643,5 +11643,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/packages/模块进度.xlsx
+++ b/packages/模块进度.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\project\js\AnJsflScript-ts\packages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D17D22-FF67-45F4-B08A-C4330A2BFA39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C27D647-0B8F-454D-8A13-67F28B8E2DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="25720" windowHeight="13800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="25720" windowHeight="13800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="原anjsfl" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="500">
   <si>
     <t xml:space="preserve">    file/</t>
   </si>
@@ -8439,6 +8439,10 @@
   </si>
   <si>
     <t>2,circular  json flatted</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>luxon</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -8561,7 +8565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -8570,7 +8574,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -8867,7 +8870,7 @@
   <dimension ref="C4:I88"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="9" max="9" width="8.6640625" style="6"/>
+    <col min="9" max="9" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
     <row r="4" spans="3:9" ht="19.5">
@@ -8884,6 +8887,9 @@
       <c r="C6" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="I6" s="5" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="7" spans="3:9" ht="19.5">
       <c r="C7" s="1" t="s">
@@ -8899,7 +8905,7 @@
       <c r="C9" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="4" t="s">
         <v>480</v>
       </c>
     </row>
@@ -8907,7 +8913,7 @@
       <c r="C10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8915,7 +8921,7 @@
       <c r="C11" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8923,7 +8929,7 @@
       <c r="C12" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8931,7 +8937,7 @@
       <c r="C13" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8944,7 +8950,7 @@
       <c r="C15" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8952,7 +8958,7 @@
       <c r="C16" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8960,7 +8966,7 @@
       <c r="C17" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8968,7 +8974,7 @@
       <c r="C18" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8976,7 +8982,7 @@
       <c r="C19" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8984,7 +8990,7 @@
       <c r="C20" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8992,7 +8998,7 @@
       <c r="C21" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9000,7 +9006,7 @@
       <c r="C22" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9008,7 +9014,7 @@
       <c r="C23" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9016,7 +9022,7 @@
       <c r="C24" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9024,7 +9030,7 @@
       <c r="C25" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9032,7 +9038,7 @@
       <c r="C26" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9040,7 +9046,7 @@
       <c r="C27" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9048,7 +9054,7 @@
       <c r="C28" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9056,7 +9062,7 @@
       <c r="C29" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9064,7 +9070,7 @@
       <c r="C30" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9072,7 +9078,7 @@
       <c r="C31" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9080,7 +9086,7 @@
       <c r="C32" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9088,7 +9094,7 @@
       <c r="C33" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9096,7 +9102,7 @@
       <c r="C34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I34" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9104,7 +9110,7 @@
       <c r="C35" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I35" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9117,7 +9123,7 @@
       <c r="C37" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="I37" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9125,7 +9131,7 @@
       <c r="C38" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I38" s="5" t="s">
+      <c r="I38" s="4" t="s">
         <v>485</v>
       </c>
     </row>
@@ -9133,7 +9139,7 @@
       <c r="C39" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="I39" s="5" t="s">
+      <c r="I39" s="4" t="s">
         <v>485</v>
       </c>
     </row>
@@ -9141,7 +9147,7 @@
       <c r="C40" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I40" s="5" t="s">
+      <c r="I40" s="4" t="s">
         <v>485</v>
       </c>
     </row>
@@ -9154,7 +9160,7 @@
       <c r="C42" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I42" s="6" t="s">
+      <c r="I42" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9162,7 +9168,7 @@
       <c r="C43" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="I43" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9195,7 +9201,7 @@
       <c r="C49" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="I49" s="6" t="s">
+      <c r="I49" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9203,7 +9209,7 @@
       <c r="C50" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I50" s="6" t="s">
+      <c r="I50" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9211,7 +9217,7 @@
       <c r="C51" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="I51" s="6" t="s">
+      <c r="I51" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9219,7 +9225,7 @@
       <c r="C52" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I52" s="6" t="s">
+      <c r="I52" s="5" t="s">
         <v>61</v>
       </c>
     </row>
@@ -9232,7 +9238,7 @@
       <c r="C54" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="I54" s="10" t="s">
+      <c r="I54" s="9" t="s">
         <v>486</v>
       </c>
     </row>
@@ -9240,7 +9246,7 @@
       <c r="C55" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I55" s="5" t="s">
+      <c r="I55" s="4" t="s">
         <v>161</v>
       </c>
     </row>
@@ -9253,7 +9259,7 @@
       <c r="C57" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="I57" s="6" t="s">
+      <c r="I57" s="4" t="s">
         <v>480</v>
       </c>
     </row>
@@ -9261,7 +9267,7 @@
       <c r="C58" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I58" s="6" t="s">
+      <c r="I58" s="4" t="s">
         <v>480</v>
       </c>
     </row>
@@ -9289,7 +9295,7 @@
       <c r="C63" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I63" s="5"/>
+      <c r="I63" s="4"/>
     </row>
     <row r="64" spans="3:9" ht="19.5">
       <c r="C64" s="1" t="s">
@@ -9305,7 +9311,7 @@
       <c r="C66" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I66" s="5" t="s">
+      <c r="I66" s="4" t="s">
         <v>160</v>
       </c>
     </row>
@@ -9313,7 +9319,7 @@
       <c r="C67" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="I67" s="5" t="s">
+      <c r="I67" s="4" t="s">
         <v>160</v>
       </c>
     </row>
@@ -9321,7 +9327,7 @@
       <c r="C68" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I68" s="5" t="s">
+      <c r="I68" s="4" t="s">
         <v>160</v>
       </c>
     </row>
@@ -9329,7 +9335,7 @@
       <c r="C69" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I69" s="5" t="s">
+      <c r="I69" s="4" t="s">
         <v>160</v>
       </c>
     </row>
@@ -9353,7 +9359,7 @@
       <c r="C73" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="I73" s="5" t="s">
+      <c r="I73" s="4" t="s">
         <v>161</v>
       </c>
     </row>
@@ -9366,7 +9372,7 @@
       <c r="C75" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="I75" s="5" t="s">
+      <c r="I75" s="4" t="s">
         <v>71</v>
       </c>
     </row>
@@ -9390,7 +9396,7 @@
       <c r="C79" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I79" s="5" t="s">
+      <c r="I79" s="4" t="s">
         <v>157</v>
       </c>
     </row>
@@ -9409,19 +9415,19 @@
       <c r="C82" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I82" s="5"/>
+      <c r="I82" s="4"/>
     </row>
     <row r="83" spans="3:9" ht="19.5">
       <c r="C83" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I83" s="5"/>
+      <c r="I83" s="4"/>
     </row>
     <row r="84" spans="3:9" ht="19.5">
       <c r="C84" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I84" s="5"/>
+      <c r="I84" s="4"/>
     </row>
     <row r="85" spans="3:9" ht="19.5">
       <c r="C85" s="1" t="s">
@@ -9432,7 +9438,7 @@
       <c r="C86" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="I86" s="5" t="s">
+      <c r="I86" s="4" t="s">
         <v>477</v>
       </c>
     </row>
@@ -9440,7 +9446,7 @@
       <c r="C87" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="I87" s="5" t="s">
+      <c r="I87" s="4" t="s">
         <v>477</v>
       </c>
     </row>
@@ -9448,7 +9454,7 @@
       <c r="C88" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I88" s="5" t="s">
+      <c r="I88" s="4" t="s">
         <v>477</v>
       </c>
     </row>
@@ -9546,7 +9552,7 @@
       <c r="D14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>62</v>
       </c>
     </row>
@@ -9554,7 +9560,7 @@
       <c r="D15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>62</v>
       </c>
     </row>
@@ -9562,7 +9568,7 @@
       <c r="D16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>62</v>
       </c>
     </row>
@@ -9570,7 +9576,7 @@
       <c r="D17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="6" t="s">
         <v>62</v>
       </c>
     </row>
@@ -9578,7 +9584,7 @@
       <c r="D18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>62</v>
       </c>
     </row>
@@ -9586,7 +9592,7 @@
       <c r="D19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="6" t="s">
         <v>62</v>
       </c>
     </row>
@@ -9612,7 +9618,7 @@
       <c r="D23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -9633,7 +9639,7 @@
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="6" t="s">
         <v>66</v>
       </c>
     </row>
@@ -9656,7 +9662,7 @@
       <c r="D30" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="6" t="s">
         <v>67</v>
       </c>
     </row>
@@ -9698,7 +9704,7 @@
       <c r="D37" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="4" t="s">
         <v>68</v>
       </c>
     </row>
@@ -9706,7 +9712,7 @@
       <c r="D38" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="7" t="s">
         <v>69</v>
       </c>
     </row>
@@ -9714,7 +9720,7 @@
       <c r="D39" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="4" t="s">
         <v>68</v>
       </c>
     </row>
@@ -9722,7 +9728,7 @@
       <c r="D40" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="4" t="s">
         <v>68</v>
       </c>
     </row>
@@ -9735,6 +9741,9 @@
       <c r="D42" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="E42" s="4" t="s">
+        <v>499</v>
+      </c>
     </row>
     <row r="43" spans="3:5" ht="21">
       <c r="D43" s="2" t="s">
@@ -9746,7 +9755,7 @@
       <c r="D44" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="7" t="s">
         <v>70</v>
       </c>
     </row>
@@ -9768,7 +9777,7 @@
       <c r="D47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="6" t="s">
         <v>72</v>
       </c>
     </row>
@@ -9781,7 +9790,7 @@
       <c r="D49" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="4" t="s">
         <v>75</v>
       </c>
     </row>
@@ -9797,7 +9806,7 @@
       <c r="D51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="7" t="s">
         <v>76</v>
       </c>
     </row>
@@ -9818,7 +9827,7 @@
       <c r="D54" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="4" t="s">
         <v>73</v>
       </c>
     </row>
@@ -9826,7 +9835,7 @@
       <c r="D55" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="E55" s="6" t="s">
         <v>72</v>
       </c>
     </row>
@@ -9834,7 +9843,7 @@
       <c r="D56" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E56" s="7" t="s">
+      <c r="E56" s="6" t="s">
         <v>72</v>
       </c>
     </row>
@@ -9842,7 +9851,7 @@
       <c r="D57" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E57" s="7" t="s">
+      <c r="E57" s="6" t="s">
         <v>72</v>
       </c>
     </row>
@@ -9870,7 +9879,7 @@
       <c r="D61" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E61" s="4" t="s">
         <v>77</v>
       </c>
     </row>
@@ -9922,50 +9931,50 @@
       <c r="C6" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="3:6" ht="19.5">
       <c r="C7" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" spans="3:6" ht="19.5">
       <c r="C8" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="9"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="3:6" ht="19.5">
       <c r="C9" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="9"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="3:6" ht="19.5">
       <c r="C10" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="3:6" ht="19.5">
       <c r="C11" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" spans="3:6" ht="20.5">
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>486</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="9"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" spans="3:6" ht="19.5">
       <c r="C13" s="1" t="s">
@@ -9976,27 +9985,27 @@
       <c r="C14" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
     </row>
     <row r="15" spans="3:6" ht="19.5">
       <c r="C15" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
     </row>
     <row r="16" spans="3:6" ht="19.5">
       <c r="C16" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
     </row>
     <row r="17" spans="3:6" ht="19.5">
       <c r="C17" s="1"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
     </row>
     <row r="18" spans="3:6" ht="19.5">
       <c r="C18" s="1" t="s">
@@ -10007,36 +10016,36 @@
       <c r="C19" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
     </row>
     <row r="20" spans="3:6" ht="19.5">
       <c r="C20" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
     </row>
     <row r="21" spans="3:6" ht="19.5">
       <c r="C21" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
     </row>
     <row r="22" spans="3:6" ht="19.5">
       <c r="C22" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
     </row>
     <row r="23" spans="3:6" ht="19.5">
       <c r="C23" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
     </row>
     <row r="24" spans="3:6" ht="19.5">
       <c r="C24" s="1" t="s">
@@ -10047,8 +10056,8 @@
       <c r="C25" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
     </row>
     <row r="26" spans="3:6" ht="19.5">
       <c r="C26" s="1" t="s">
@@ -10059,41 +10068,41 @@
       <c r="C27" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
     </row>
     <row r="28" spans="3:6" ht="19.5">
       <c r="C28" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F28" s="9"/>
+      <c r="F28" s="8"/>
     </row>
     <row r="29" spans="3:6" ht="19.5">
       <c r="C29" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
     </row>
     <row r="30" spans="3:6" ht="19.5">
       <c r="C30" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="E30" s="5"/>
+      <c r="E30" s="4"/>
     </row>
     <row r="31" spans="3:6" ht="19.5">
       <c r="C31" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
     </row>
     <row r="32" spans="3:6" ht="19.5">
       <c r="C32" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -10106,11 +10115,11 @@
   <dimension ref="C4:H294"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="7" max="7" width="8.6640625" style="6"/>
+    <col min="7" max="7" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
     <row r="4" spans="3:8">
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>474</v>
       </c>
       <c r="H4" t="s">
@@ -11579,64 +11588,64 @@
   <dimension ref="C4:E13"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="5" max="5" width="8.6640625" style="6"/>
+    <col min="5" max="5" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
     <row r="4" spans="3:5" ht="14.5">
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>495</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="3:5" ht="14.5">
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="4"/>
     </row>
     <row r="6" spans="3:5" ht="14.5">
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="4"/>
     </row>
     <row r="7" spans="3:5" ht="14.5">
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>490</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8" spans="3:5" ht="14.5">
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>491</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="4"/>
     </row>
     <row r="9" spans="3:5" ht="14.5">
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" spans="3:5" ht="14.5">
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>497</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" spans="3:5" ht="14.5">
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="12" spans="3:5" ht="14.5">
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="10" t="s">
         <v>493</v>
       </c>
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="3:5" ht="14.5">
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>494</v>
       </c>
     </row>

--- a/packages/模块进度.xlsx
+++ b/packages/模块进度.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\project\js\AnJsflScript-ts\packages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C27D647-0B8F-454D-8A13-67F28B8E2DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5E1EE3-49B0-46D8-9F0A-12B63B6E80D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="25720" windowHeight="13800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="25720" windowHeight="13800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="原anjsfl" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="497">
   <si>
     <t xml:space="preserve">    file/</t>
   </si>
@@ -8387,40 +8387,27 @@
     <t>console.table</t>
   </si>
   <si>
-    <t>3, weakmap es6-collections</t>
-  </si>
-  <si>
-    <t>4,intl formatjs</t>
-  </si>
-  <si>
-    <t>5，progress</t>
-  </si>
-  <si>
     <t>8,xul测试</t>
   </si>
   <si>
-    <t>9.test tape node test</t>
-  </si>
-  <si>
     <t>10.Context 重写</t>
   </si>
   <si>
-    <t>1,action utility-types</t>
+    <t>luxon</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">6,storejs </t>
+      <t xml:space="preserve">console.stack </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF1F0909"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>改为局部，不要</t>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>有</t>
     </r>
     <r>
       <rPr>
@@ -8429,20 +8416,111 @@
         <rFont val="PT Serif"/>
         <family val="1"/>
       </rPr>
-      <t>cookie</t>
+      <t>bug</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F0909"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，输出只有序号，没有内容</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>7,reflect,proxy harmony-reflect</t>
+    <t>console.stack 保存数据不合理，需要重新设计</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2,circular  json flatted</t>
+    <r>
+      <t xml:space="preserve">await </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F0909"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>暂时转译的代码无法正常运行，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F0909"/>
+        <rFont val="PT Serif"/>
+        <family val="1"/>
+      </rPr>
+      <t>promise</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F0909"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>可以正常运行，需要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F0909"/>
+        <rFont val="PT Serif"/>
+        <family val="2"/>
+      </rPr>
+      <t>console.stack</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F0909"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>修复完成，在修</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F0909"/>
+        <rFont val="PT Serif"/>
+        <family val="2"/>
+      </rPr>
+      <t>bug</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>luxon</t>
+    <t>在节日时，发送祝福，暂定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Tips</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F0909"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>修改为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F0909"/>
+        <rFont val="PT Serif"/>
+        <family val="1"/>
+      </rPr>
+      <t>packages</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -8450,7 +8528,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8516,8 +8594,21 @@
     <font>
       <sz val="10"/>
       <color rgb="FF1F0909"/>
+      <name val="等线"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F0909"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F0909"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -9742,7 +9833,7 @@
         <v>34</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
     </row>
     <row r="43" spans="3:5" ht="21">
@@ -11585,68 +11676,45 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F352BAE6-08AF-4793-89CF-B233BC25CAF3}">
-  <dimension ref="C4:E13"/>
+  <dimension ref="C4:E11"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="5" max="5" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:5" ht="14.5">
+    <row r="4" spans="3:3" ht="14.5">
       <c r="C4" s="10" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" ht="14.5">
+      <c r="C5" s="10" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="7" spans="3:3" ht="14.5">
+      <c r="C7" s="10" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3">
+      <c r="C8" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" ht="14.5">
+      <c r="C9" s="10" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="10" spans="3:3">
+      <c r="C10" t="s">
         <v>495</v>
       </c>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="3:5" ht="14.5">
-      <c r="C5" s="10" t="s">
-        <v>498</v>
-      </c>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="3:5" ht="14.5">
-      <c r="C6" s="10" t="s">
-        <v>489</v>
-      </c>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="3:5" ht="14.5">
-      <c r="C7" s="10" t="s">
-        <v>490</v>
-      </c>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="3:5" ht="14.5">
-      <c r="C8" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="3:5" ht="14.5">
-      <c r="C9" s="10" t="s">
+    </row>
+    <row r="11" spans="3:3" ht="14.5">
+      <c r="C11" s="10" t="s">
         <v>496</v>
-      </c>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="3:5" ht="14.5">
-      <c r="C10" s="10" t="s">
-        <v>497</v>
-      </c>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="3:5" ht="14.5">
-      <c r="C11" s="10" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="12" spans="3:5" ht="14.5">
-      <c r="C12" s="10" t="s">
-        <v>493</v>
-      </c>
-      <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="3:5" ht="14.5">
-      <c r="C13" s="10" t="s">
-        <v>494</v>
       </c>
     </row>
   </sheetData>

--- a/packages/模块进度.xlsx
+++ b/packages/模块进度.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\project\js\AnJsflScript-ts\packages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5E1EE3-49B0-46D8-9F0A-12B63B6E80D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816C11DD-E20D-48E1-8A6B-0BCAB4ABB37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="25720" windowHeight="13800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11682,40 +11682,44 @@
     <col min="5" max="5" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:3" ht="14.5">
+    <row r="4" spans="3:5" ht="14.5">
       <c r="C4" s="10" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="5" spans="3:3" ht="14.5">
+    <row r="5" spans="3:5" ht="14.5">
       <c r="C5" s="10" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="7" spans="3:3" ht="14.5">
+    <row r="7" spans="3:5" ht="14.5">
       <c r="C7" s="10" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="8" spans="3:3">
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="3:5">
       <c r="C8" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="9" spans="3:3" ht="14.5">
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="3:5" ht="14.5">
       <c r="C9" s="10" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="10" spans="3:3">
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="3:5">
       <c r="C10" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="11" spans="3:3" ht="14.5">
+    <row r="11" spans="3:5" ht="14.5">
       <c r="C11" s="10" t="s">
         <v>496</v>
       </c>
+      <c r="E11" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/packages/模块进度.xlsx
+++ b/packages/模块进度.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\project\js\AnJsflScript-ts\packages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816C11DD-E20D-48E1-8A6B-0BCAB4ABB37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9693ADAB-C409-402E-A54C-FB8536239B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="25720" windowHeight="13800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/packages/模块进度.xlsx
+++ b/packages/模块进度.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\project\js\AnJsflScript-ts\packages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9693ADAB-C409-402E-A54C-FB8536239B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1543A22-EFD6-4FAD-BEA3-7CE927616A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="25720" windowHeight="13800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="500">
   <si>
     <t xml:space="preserve">    file/</t>
   </si>
@@ -8523,12 +8523,35 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t>inspect</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>加日志</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>重构 interface重构</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> process重构</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8611,6 +8634,19 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -8656,7 +8692,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -8678,6 +8714,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -11676,7 +11713,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F352BAE6-08AF-4793-89CF-B233BC25CAF3}">
-  <dimension ref="C4:E11"/>
+  <dimension ref="C4:E15"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="5" max="5" width="8.6640625" style="5"/>
@@ -11691,6 +11728,7 @@
       <c r="C5" s="10" t="s">
         <v>490</v>
       </c>
+      <c r="E5" s="4"/>
     </row>
     <row r="7" spans="3:5" ht="14.5">
       <c r="C7" s="10" t="s">
@@ -11720,6 +11758,22 @@
         <v>496</v>
       </c>
       <c r="E11" s="4"/>
+    </row>
+    <row r="13" spans="3:5" ht="14.5">
+      <c r="C13" s="11" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5">
+      <c r="C14" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5">
+      <c r="C15" t="s">
+        <v>499</v>
+      </c>
+      <c r="E15" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
